--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DSA\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB77959-D6B2-4519-84E4-ACA7A8A45998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="2988" yWindow="2100" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -51,10 +60,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/remove-duplicates-from-sorted-list/</t>
     </r>
@@ -65,10 +74,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/remove-duplicates-from-sorted-array-ii/</t>
     </r>
@@ -85,10 +94,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/3sum/</t>
     </r>
@@ -99,10 +108,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/3sum-closest/</t>
     </r>
@@ -119,10 +128,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/subarray-product-less-than-k/</t>
     </r>
@@ -139,10 +148,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/4sum/</t>
     </r>
@@ -153,10 +162,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/backspace-string-compare/</t>
     </r>
@@ -167,10 +176,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/shortest-unsorted-continuous-subarray/</t>
     </r>
@@ -178,10 +187,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://www.ideserve.co.in/learn/minimum-length-subarray-sorting-which-results-in-sorted-array</t>
     </r>
@@ -195,10 +204,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/linked-list-cycle/</t>
     </r>
@@ -209,10 +218,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/linked-list-cycle-ii/</t>
     </r>
@@ -223,10 +232,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/happy-number/</t>
     </r>
@@ -243,10 +252,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/middle-of-the-linked-list/</t>
     </r>
@@ -257,10 +266,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/palindrome-linked-list/</t>
     </r>
@@ -271,10 +280,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/reorder-list/</t>
     </r>
@@ -285,10 +294,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/circular-array-loop/</t>
     </r>
@@ -320,10 +329,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/fruit-into-baskets/</t>
     </r>
@@ -334,10 +343,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/longest-substring-without-repeating-characters/</t>
     </r>
@@ -348,10 +357,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/longest-repeating-character-replacement/</t>
     </r>
@@ -362,10 +371,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/max-consecutive-ones-iii/</t>
     </r>
@@ -385,10 +394,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/permutation-in-string/</t>
     </r>
@@ -399,10 +408,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/find-all-anagrams-in-a-string/</t>
     </r>
@@ -518,10 +527,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://www.geeksforgeeks.org/check-if-any-two-intervals-overlap-among-a-given-set-of-intervals/</t>
     </r>
@@ -538,10 +547,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://www.geeksforgeeks.org/maximum-cpu-load-from-the-given-list-of-jobs/</t>
     </r>
@@ -552,10 +561,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://www.codertrain.co/employee-free-time</t>
     </r>
@@ -569,10 +578,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/reverse-linked-list/</t>
     </r>
@@ -583,10 +592,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/reverse-linked-list-ii/</t>
     </r>
@@ -603,10 +612,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/reverse-nodes-in-k-group/</t>
     </r>
@@ -623,10 +632,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/rotate-list/</t>
     </r>
@@ -646,10 +655,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/valid-parentheses/description/</t>
     </r>
@@ -669,10 +678,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/daily-temperatures/</t>
     </r>
@@ -683,10 +692,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/remove-nodes-from-linked-list/</t>
     </r>
@@ -697,10 +706,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/remove-all-adjacent-duplicates-in-string-ii/</t>
     </r>
@@ -717,10 +726,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/remove-k-digits/</t>
     </r>
@@ -734,10 +743,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/first-unique-character-in-a-string/</t>
     </r>
@@ -748,10 +757,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/maximum-number-of-balloons/</t>
     </r>
@@ -762,10 +771,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/longest-palindrome/</t>
     </r>
@@ -776,10 +785,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
       </rPr>
       <t>https://leetcode.com/problems/ransom-note/</t>
     </r>
@@ -1469,10 +1478,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="16">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="17">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1480,94 +1489,105 @@
     <font>
       <b/>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF1155CC"/>
+      <name val="Calibri, sans-serif"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1629,9 +1649,21 @@
         <bgColor rgb="FFE69138"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -1645,132 +1677,79 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="37">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="10" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="11" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1960,24 +1939,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E191"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.63"/>
-    <col customWidth="1" min="2" max="2" width="65.5"/>
-    <col customWidth="1" min="3" max="3" width="77.25"/>
-    <col customWidth="1" min="4" max="4" width="53.13"/>
-    <col customWidth="1" min="5" max="5" width="30.5"/>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="2" max="2" width="65.44140625" customWidth="1"/>
+    <col min="3" max="3" width="77.21875" customWidth="1"/>
+    <col min="4" max="4" width="53.109375" customWidth="1"/>
+    <col min="5" max="5" width="30.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="14.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1986,7 +1968,7 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="14.4">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2003,7 +1985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
       <c r="A3" s="6"/>
       <c r="B3" s="7" t="s">
         <v>6</v>
@@ -2012,8 +1994,8 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
     </row>
-    <row r="4">
-      <c r="A4" s="6"/>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A4" s="33"/>
       <c r="B4" s="9" t="s">
         <v>7</v>
       </c>
@@ -2023,7 +2005,7 @@
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1">
       <c r="A5" s="6"/>
       <c r="B5" s="9" t="s">
         <v>9</v>
@@ -2034,8 +2016,8 @@
       <c r="D5" s="12"/>
       <c r="E5" s="13"/>
     </row>
-    <row r="6">
-      <c r="A6" s="6"/>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A6" s="33"/>
       <c r="B6" s="9" t="s">
         <v>11</v>
       </c>
@@ -2049,8 +2031,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6"/>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A7" s="33"/>
       <c r="B7" s="9" t="s">
         <v>15</v>
       </c>
@@ -2060,8 +2042,8 @@
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
     </row>
-    <row r="8">
-      <c r="A8" s="6"/>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A8" s="33"/>
       <c r="B8" s="9" t="s">
         <v>17</v>
       </c>
@@ -2071,8 +2053,8 @@
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
     </row>
-    <row r="9">
-      <c r="A9" s="6"/>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A9" s="33"/>
       <c r="B9" s="9" t="s">
         <v>19</v>
       </c>
@@ -2082,8 +2064,8 @@
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10">
-      <c r="A10" s="6"/>
+    <row r="10" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A10" s="33"/>
       <c r="B10" s="9" t="s">
         <v>21</v>
       </c>
@@ -2093,9 +2075,9 @@
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1">
       <c r="A11" s="6"/>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="11" t="s">
@@ -2104,7 +2086,7 @@
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="9" t="s">
         <v>25</v>
@@ -2115,9 +2097,9 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1">
       <c r="A13" s="6"/>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="11" t="s">
@@ -2126,9 +2108,9 @@
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1">
       <c r="A14" s="6"/>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="11" t="s">
@@ -2137,19 +2119,20 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1">
       <c r="A15" s="6"/>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="35" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16">
+      <c r="E15" s="36"/>
+    </row>
+    <row r="16" spans="1:5" ht="14.4">
       <c r="A16" s="6"/>
       <c r="B16" s="7" t="s">
         <v>34</v>
@@ -2158,8 +2141,8 @@
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
     </row>
-    <row r="17">
-      <c r="A17" s="6"/>
+    <row r="17" spans="1:5" ht="14.4">
+      <c r="A17" s="33"/>
       <c r="B17" s="9" t="s">
         <v>35</v>
       </c>
@@ -2169,8 +2152,8 @@
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
     </row>
-    <row r="18">
-      <c r="A18" s="6"/>
+    <row r="18" spans="1:5" ht="14.4">
+      <c r="A18" s="33"/>
       <c r="B18" s="9" t="s">
         <v>37</v>
       </c>
@@ -2180,8 +2163,8 @@
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
     </row>
-    <row r="19">
-      <c r="A19" s="6"/>
+    <row r="19" spans="1:5" ht="14.4">
+      <c r="A19" s="33"/>
       <c r="B19" s="9" t="s">
         <v>39</v>
       </c>
@@ -2191,8 +2174,8 @@
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
     </row>
-    <row r="20">
-      <c r="A20" s="6"/>
+    <row r="20" spans="1:5" ht="14.4">
+      <c r="A20" s="33"/>
       <c r="B20" s="9" t="s">
         <v>41</v>
       </c>
@@ -2202,8 +2185,8 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
     </row>
-    <row r="21">
-      <c r="A21" s="6"/>
+    <row r="21" spans="1:5" ht="14.4">
+      <c r="A21" s="33"/>
       <c r="B21" s="9" t="s">
         <v>43</v>
       </c>
@@ -2213,9 +2196,9 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5" ht="14.4">
       <c r="A22" s="6"/>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="6" t="s">
         <v>45</v>
       </c>
       <c r="C22" s="11" t="s">
@@ -2224,9 +2207,9 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5" ht="14.4">
       <c r="A23" s="6"/>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C23" s="11" t="s">
@@ -2235,9 +2218,9 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5" ht="14.4">
       <c r="A24" s="6"/>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="6" t="s">
         <v>49</v>
       </c>
       <c r="C24" s="11" t="s">
@@ -2246,7 +2229,7 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5" ht="14.4">
       <c r="A25" s="6"/>
       <c r="B25" s="7" t="s">
         <v>51</v>
@@ -2255,18 +2238,18 @@
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5" ht="14.4">
       <c r="A26" s="6"/>
       <c r="B26" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="16" t="s">
         <v>53</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5" ht="14.4">
       <c r="A27" s="6"/>
       <c r="B27" s="9" t="s">
         <v>54</v>
@@ -2277,7 +2260,7 @@
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5" ht="14.4">
       <c r="A28" s="6"/>
       <c r="B28" s="9" t="s">
         <v>56</v>
@@ -2288,7 +2271,7 @@
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5" ht="14.4">
       <c r="A29" s="6"/>
       <c r="B29" s="9" t="s">
         <v>58</v>
@@ -2299,7 +2282,7 @@
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5" ht="14.4">
       <c r="A30" s="6"/>
       <c r="B30" s="9" t="s">
         <v>60</v>
@@ -2310,7 +2293,7 @@
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5" ht="14.4">
       <c r="A31" s="6"/>
       <c r="B31" s="9" t="s">
         <v>62</v>
@@ -2321,7 +2304,7 @@
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5" ht="14.4">
       <c r="A32" s="6"/>
       <c r="B32" s="9" t="s">
         <v>64</v>
@@ -2332,7 +2315,7 @@
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5" ht="14.4">
       <c r="A33" s="6"/>
       <c r="B33" s="9" t="s">
         <v>66</v>
@@ -2343,7 +2326,7 @@
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:5" ht="14.4">
       <c r="A34" s="6"/>
       <c r="B34" s="9" t="s">
         <v>67</v>
@@ -2354,9 +2337,9 @@
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:5" ht="14.4">
       <c r="A35" s="6"/>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="6" t="s">
         <v>69</v>
       </c>
       <c r="C35" s="11" t="s">
@@ -2365,9 +2348,9 @@
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:5" ht="14.4">
       <c r="A36" s="6"/>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C36" s="11" t="s">
@@ -2376,9 +2359,9 @@
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:5" ht="14.4">
       <c r="A37" s="6"/>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C37" s="14" t="s">
@@ -2387,7 +2370,7 @@
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:5" ht="14.4">
       <c r="A38" s="6"/>
       <c r="B38" s="7" t="s">
         <v>75</v>
@@ -2396,73 +2379,73 @@
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:5" ht="14.4">
       <c r="A39" s="6"/>
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="16" t="s">
         <v>77</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:5" ht="14.4">
       <c r="A40" s="6"/>
       <c r="B40" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="16" t="s">
         <v>79</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:5" ht="14.4">
       <c r="A41" s="6"/>
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="16" t="s">
         <v>81</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:5" ht="14.4">
       <c r="A42" s="6"/>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="16" t="s">
         <v>83</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:5" ht="14.4">
       <c r="A43" s="6"/>
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="16" t="s">
         <v>85</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:5" ht="14.4">
       <c r="A44" s="6"/>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="16" t="s">
         <v>87</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:5" ht="14.4">
       <c r="A45" s="6"/>
       <c r="B45" s="7" t="s">
         <v>88</v>
@@ -2471,73 +2454,73 @@
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:5" ht="14.4">
       <c r="A46" s="6"/>
-      <c r="B46" s="18" t="s">
+      <c r="B46" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="16" t="s">
         <v>90</v>
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:5" ht="14.4">
       <c r="A47" s="6"/>
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="16" t="s">
         <v>92</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:5" ht="14.4">
       <c r="A48" s="6"/>
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="17" t="s">
+      <c r="C48" s="16" t="s">
         <v>94</v>
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:5" ht="14.4">
       <c r="A49" s="6"/>
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C49" s="16" t="s">
         <v>96</v>
       </c>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:5" ht="14.4">
       <c r="A50" s="6"/>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="16" t="s">
         <v>98</v>
       </c>
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:5" ht="14.4">
       <c r="A51" s="6"/>
-      <c r="B51" s="19" t="s">
+      <c r="B51" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="17" t="s">
+      <c r="C51" s="16" t="s">
         <v>100</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:5" ht="14.4">
       <c r="A52" s="6"/>
       <c r="B52" s="7" t="s">
         <v>101</v>
@@ -2546,7 +2529,7 @@
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:5" ht="14.4">
       <c r="A53" s="6"/>
       <c r="B53" s="9" t="s">
         <v>102</v>
@@ -2557,7 +2540,7 @@
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:5" ht="14.4">
       <c r="A54" s="6"/>
       <c r="B54" s="9" t="s">
         <v>104</v>
@@ -2568,7 +2551,7 @@
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:5" ht="14.4">
       <c r="A55" s="6"/>
       <c r="B55" s="9" t="s">
         <v>106</v>
@@ -2579,17 +2562,18 @@
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:5" ht="14.4">
       <c r="A56" s="6"/>
       <c r="B56" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="35" t="s">
         <v>109</v>
       </c>
+      <c r="D56" s="36"/>
       <c r="E56" s="8"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:5" ht="14.4">
       <c r="A57" s="6"/>
       <c r="B57" s="9" t="s">
         <v>110</v>
@@ -2600,9 +2584,9 @@
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:5" ht="14.4">
       <c r="A58" s="6"/>
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="6" t="s">
         <v>112</v>
       </c>
       <c r="C58" s="11" t="s">
@@ -2611,9 +2595,9 @@
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:5" ht="14.4">
       <c r="A59" s="6"/>
-      <c r="B59" s="15" t="s">
+      <c r="B59" s="6" t="s">
         <v>114</v>
       </c>
       <c r="C59" s="11" t="s">
@@ -2622,7 +2606,7 @@
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:5" ht="14.4">
       <c r="A60" s="6"/>
       <c r="B60" s="7" t="s">
         <v>116</v>
@@ -2631,7 +2615,7 @@
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:5" ht="14.4">
       <c r="A61" s="6"/>
       <c r="B61" s="9" t="s">
         <v>117</v>
@@ -2642,7 +2626,7 @@
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:5" ht="14.4">
       <c r="A62" s="6"/>
       <c r="B62" s="9" t="s">
         <v>119</v>
@@ -2653,7 +2637,7 @@
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:5" ht="14.4">
       <c r="A63" s="6"/>
       <c r="B63" s="9" t="s">
         <v>121</v>
@@ -2664,7 +2648,7 @@
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:5" ht="14.4">
       <c r="A64" s="6"/>
       <c r="B64" s="9" t="s">
         <v>123</v>
@@ -2675,9 +2659,9 @@
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:5" ht="14.4">
       <c r="A65" s="6"/>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="6" t="s">
         <v>125</v>
       </c>
       <c r="C65" s="11" t="s">
@@ -2686,7 +2670,7 @@
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:5" ht="14.4">
       <c r="A66" s="6"/>
       <c r="B66" s="9" t="s">
         <v>127</v>
@@ -2697,7 +2681,7 @@
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:5" ht="14.4">
       <c r="A67" s="6"/>
       <c r="B67" s="7" t="s">
         <v>129</v>
@@ -2706,9 +2690,9 @@
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:5" ht="14.4">
       <c r="A68" s="6"/>
-      <c r="B68" s="20" t="s">
+      <c r="B68" s="19" t="s">
         <v>130</v>
       </c>
       <c r="C68" s="11" t="s">
@@ -2717,7 +2701,7 @@
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:5" ht="14.4">
       <c r="A69" s="6"/>
       <c r="B69" s="9" t="s">
         <v>132</v>
@@ -2728,7 +2712,7 @@
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:5" ht="14.4">
       <c r="A70" s="6"/>
       <c r="B70" s="9" t="s">
         <v>134</v>
@@ -2737,7 +2721,7 @@
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:5" ht="14.4">
       <c r="A71" s="6"/>
       <c r="B71" s="9" t="s">
         <v>135</v>
@@ -2748,7 +2732,7 @@
       <c r="D71" s="13"/>
       <c r="E71" s="13"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:5" ht="14.4">
       <c r="A72" s="6"/>
       <c r="B72" s="9" t="s">
         <v>137</v>
@@ -2759,9 +2743,9 @@
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:5" ht="14.4">
       <c r="A73" s="6"/>
-      <c r="B73" s="15" t="s">
+      <c r="B73" s="6" t="s">
         <v>139</v>
       </c>
       <c r="C73" s="11" t="s">
@@ -2770,7 +2754,7 @@
       <c r="D73" s="8"/>
       <c r="E73" s="8"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:5" ht="14.4">
       <c r="A74" s="6"/>
       <c r="B74" s="9" t="s">
         <v>141</v>
@@ -2781,9 +2765,9 @@
       <c r="D74" s="8"/>
       <c r="E74" s="8"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:5" ht="14.4">
       <c r="A75" s="6"/>
-      <c r="B75" s="15" t="s">
+      <c r="B75" s="6" t="s">
         <v>143</v>
       </c>
       <c r="C75" s="11" t="s">
@@ -2792,9 +2776,9 @@
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:5" ht="14.4">
       <c r="A76" s="6"/>
-      <c r="B76" s="15" t="s">
+      <c r="B76" s="6" t="s">
         <v>145</v>
       </c>
       <c r="C76" s="11" t="s">
@@ -2803,7 +2787,7 @@
       <c r="D76" s="8"/>
       <c r="E76" s="8"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:5" ht="14.4">
       <c r="A77" s="6"/>
       <c r="B77" s="7" t="s">
         <v>147</v>
@@ -2812,8 +2796,8 @@
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
     </row>
-    <row r="78">
-      <c r="A78" s="6"/>
+    <row r="78" spans="1:5" ht="14.4">
+      <c r="A78" s="33"/>
       <c r="B78" s="9" t="s">
         <v>148</v>
       </c>
@@ -2823,8 +2807,8 @@
       <c r="D78" s="8"/>
       <c r="E78" s="8"/>
     </row>
-    <row r="79">
-      <c r="A79" s="6"/>
+    <row r="79" spans="1:5" ht="14.4">
+      <c r="A79" s="33"/>
       <c r="B79" s="9" t="s">
         <v>150</v>
       </c>
@@ -2834,8 +2818,8 @@
       <c r="D79" s="8"/>
       <c r="E79" s="8"/>
     </row>
-    <row r="80">
-      <c r="A80" s="6"/>
+    <row r="80" spans="1:5" ht="14.4">
+      <c r="A80" s="33"/>
       <c r="B80" s="9" t="s">
         <v>152</v>
       </c>
@@ -2845,8 +2829,8 @@
       <c r="D80" s="8"/>
       <c r="E80" s="8"/>
     </row>
-    <row r="81">
-      <c r="A81" s="6"/>
+    <row r="81" spans="1:5" ht="14.4">
+      <c r="A81" s="33"/>
       <c r="B81" s="9" t="s">
         <v>154</v>
       </c>
@@ -2856,17 +2840,17 @@
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:5" ht="14.4">
       <c r="A82" s="6"/>
       <c r="B82" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C82" s="21"/>
+      <c r="C82" s="20"/>
       <c r="D82" s="8"/>
       <c r="E82" s="8"/>
     </row>
-    <row r="83">
-      <c r="A83" s="6"/>
+    <row r="83" spans="1:5" ht="14.4">
+      <c r="A83" s="33"/>
       <c r="B83" s="9" t="s">
         <v>157</v>
       </c>
@@ -2876,8 +2860,8 @@
       <c r="D83" s="8"/>
       <c r="E83" s="8"/>
     </row>
-    <row r="84">
-      <c r="A84" s="6"/>
+    <row r="84" spans="1:5" ht="14.4">
+      <c r="A84" s="33"/>
       <c r="B84" s="9" t="s">
         <v>159</v>
       </c>
@@ -2887,8 +2871,8 @@
       <c r="D84" s="8"/>
       <c r="E84" s="8"/>
     </row>
-    <row r="85">
-      <c r="A85" s="6"/>
+    <row r="85" spans="1:5" ht="14.4">
+      <c r="A85" s="33"/>
       <c r="B85" s="9" t="s">
         <v>161</v>
       </c>
@@ -2898,7 +2882,7 @@
       <c r="D85" s="8"/>
       <c r="E85" s="8"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:5" ht="14.4">
       <c r="A86" s="6"/>
       <c r="B86" s="9" t="s">
         <v>163</v>
@@ -2909,9 +2893,9 @@
       <c r="D86" s="8"/>
       <c r="E86" s="8"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:5" ht="14.4">
       <c r="A87" s="6"/>
-      <c r="B87" s="15" t="s">
+      <c r="B87" s="6" t="s">
         <v>165</v>
       </c>
       <c r="C87" s="11" t="s">
@@ -2920,8 +2904,8 @@
       <c r="D87" s="8"/>
       <c r="E87" s="8"/>
     </row>
-    <row r="88">
-      <c r="A88" s="6"/>
+    <row r="88" spans="1:5" ht="14.4">
+      <c r="A88" s="33"/>
       <c r="B88" s="9" t="s">
         <v>167</v>
       </c>
@@ -2931,9 +2915,9 @@
       <c r="D88" s="8"/>
       <c r="E88" s="8"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:5" ht="14.4">
       <c r="A89" s="6"/>
-      <c r="B89" s="15" t="s">
+      <c r="B89" s="6" t="s">
         <v>169</v>
       </c>
       <c r="C89" s="11" t="s">
@@ -2942,8 +2926,8 @@
       <c r="D89" s="8"/>
       <c r="E89" s="8"/>
     </row>
-    <row r="90">
-      <c r="A90" s="6"/>
+    <row r="90" spans="1:5" ht="14.4">
+      <c r="A90" s="33"/>
       <c r="B90" s="9" t="s">
         <v>171</v>
       </c>
@@ -2953,7 +2937,7 @@
       <c r="D90" s="8"/>
       <c r="E90" s="8"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:5" ht="14.4">
       <c r="A91" s="6"/>
       <c r="B91" s="9" t="s">
         <v>173</v>
@@ -2964,7 +2948,7 @@
       <c r="D91" s="8"/>
       <c r="E91" s="8"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:5" ht="14.4">
       <c r="A92" s="6"/>
       <c r="B92" s="9" t="s">
         <v>175</v>
@@ -2975,7 +2959,7 @@
       <c r="D92" s="8"/>
       <c r="E92" s="8"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:5" ht="14.4">
       <c r="A93" s="6"/>
       <c r="B93" s="9" t="s">
         <v>177</v>
@@ -2986,9 +2970,9 @@
       <c r="D93" s="8"/>
       <c r="E93" s="8"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:5" ht="14.4">
       <c r="A94" s="6"/>
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="6" t="s">
         <v>179</v>
       </c>
       <c r="C94" s="11" t="s">
@@ -2997,7 +2981,7 @@
       <c r="D94" s="8"/>
       <c r="E94" s="8"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:5" ht="14.4">
       <c r="A95" s="6"/>
       <c r="B95" s="9" t="s">
         <v>181</v>
@@ -3008,9 +2992,9 @@
       <c r="D95" s="8"/>
       <c r="E95" s="8"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:5" ht="14.4">
       <c r="A96" s="6"/>
-      <c r="B96" s="22" t="s">
+      <c r="B96" s="21" t="s">
         <v>183</v>
       </c>
       <c r="C96" s="11" t="s">
@@ -3019,9 +3003,9 @@
       <c r="D96" s="8"/>
       <c r="E96" s="8"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:5" ht="14.4">
       <c r="A97" s="6"/>
-      <c r="B97" s="15" t="s">
+      <c r="B97" s="6" t="s">
         <v>185</v>
       </c>
       <c r="C97" s="11" t="s">
@@ -3030,9 +3014,9 @@
       <c r="D97" s="8"/>
       <c r="E97" s="8"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:5" ht="14.4">
       <c r="A98" s="6"/>
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="6" t="s">
         <v>187</v>
       </c>
       <c r="C98" s="11" t="s">
@@ -3041,7 +3025,7 @@
       <c r="D98" s="8"/>
       <c r="E98" s="8"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:5" ht="14.4">
       <c r="A99" s="6"/>
       <c r="B99" s="9" t="s">
         <v>189</v>
@@ -3052,9 +3036,9 @@
       <c r="D99" s="8"/>
       <c r="E99" s="8"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:5" ht="14.4">
       <c r="A100" s="6"/>
-      <c r="B100" s="15" t="s">
+      <c r="B100" s="6" t="s">
         <v>191</v>
       </c>
       <c r="C100" s="14" t="s">
@@ -3063,7 +3047,7 @@
       <c r="D100" s="8"/>
       <c r="E100" s="8"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:5" ht="14.4">
       <c r="A101" s="6"/>
       <c r="B101" s="9" t="s">
         <v>193</v>
@@ -3074,7 +3058,7 @@
       <c r="D101" s="8"/>
       <c r="E101" s="8"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:5" ht="14.4">
       <c r="A102" s="6"/>
       <c r="B102" s="9" t="s">
         <v>195</v>
@@ -3085,7 +3069,7 @@
       <c r="D102" s="8"/>
       <c r="E102" s="8"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:5" ht="14.4">
       <c r="A103" s="6"/>
       <c r="B103" s="9" t="s">
         <v>197</v>
@@ -3096,7 +3080,7 @@
       <c r="D103" s="8"/>
       <c r="E103" s="8"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:5" ht="14.4">
       <c r="A104" s="6"/>
       <c r="B104" s="9" t="s">
         <v>199</v>
@@ -3107,9 +3091,9 @@
       <c r="D104" s="8"/>
       <c r="E104" s="8"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:5" ht="14.4">
       <c r="A105" s="6"/>
-      <c r="B105" s="15" t="s">
+      <c r="B105" s="6" t="s">
         <v>201</v>
       </c>
       <c r="C105" s="14" t="s">
@@ -3118,7 +3102,7 @@
       <c r="D105" s="8"/>
       <c r="E105" s="8"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:5" ht="14.4">
       <c r="A106" s="6"/>
       <c r="B106" s="7" t="s">
         <v>203</v>
@@ -3127,204 +3111,204 @@
       <c r="D106" s="8"/>
       <c r="E106" s="8"/>
     </row>
-    <row r="107">
-      <c r="A107" s="23" t="s">
+    <row r="107" spans="1:5" ht="14.4">
+      <c r="A107" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="B107" s="24" t="s">
+      <c r="B107" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="C107" s="25" t="s">
+      <c r="C107" s="24" t="s">
         <v>206</v>
       </c>
       <c r="D107" s="8"/>
       <c r="E107" s="8"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:5" ht="14.4">
       <c r="A108" s="6"/>
-      <c r="B108" s="24" t="s">
+      <c r="B108" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="C108" s="25" t="s">
+      <c r="C108" s="24" t="s">
         <v>208</v>
       </c>
       <c r="D108" s="8"/>
       <c r="E108" s="8"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:5" ht="14.4">
       <c r="A109" s="6"/>
-      <c r="B109" s="24" t="s">
+      <c r="B109" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="C109" s="25" t="s">
+      <c r="C109" s="24" t="s">
         <v>210</v>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="8"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:5" ht="14.4">
       <c r="A110" s="6"/>
-      <c r="B110" s="24" t="s">
+      <c r="B110" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="C110" s="25" t="s">
+      <c r="C110" s="24" t="s">
         <v>212</v>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8"/>
     </row>
-    <row r="111">
-      <c r="A111" s="23" t="s">
+    <row r="111" spans="1:5" ht="14.4">
+      <c r="A111" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="B111" s="26" t="s">
+      <c r="B111" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="C111" s="25" t="s">
+      <c r="C111" s="24" t="s">
         <v>215</v>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:5" ht="14.4">
       <c r="A112" s="6"/>
-      <c r="B112" s="26" t="s">
+      <c r="B112" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="C112" s="17" t="s">
+      <c r="C112" s="16" t="s">
         <v>217</v>
       </c>
       <c r="D112" s="8"/>
       <c r="E112" s="8"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:5" ht="14.4">
       <c r="A113" s="6"/>
-      <c r="B113" s="26" t="s">
+      <c r="B113" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="C113" s="17" t="s">
+      <c r="C113" s="16" t="s">
         <v>219</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8"/>
     </row>
-    <row r="114">
-      <c r="A114" s="23" t="s">
+    <row r="114" spans="1:5" ht="14.4">
+      <c r="A114" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="B114" s="27" t="s">
+      <c r="B114" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="C114" s="25" t="s">
+      <c r="C114" s="24" t="s">
         <v>222</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:5" ht="14.4">
       <c r="A115" s="6"/>
-      <c r="B115" s="27" t="s">
+      <c r="B115" s="26" t="s">
         <v>223</v>
       </c>
-      <c r="C115" s="17" t="s">
+      <c r="C115" s="16" t="s">
         <v>198</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8"/>
     </row>
-    <row r="116">
-      <c r="A116" s="23" t="s">
+    <row r="116" spans="1:5" ht="14.4">
+      <c r="A116" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="B116" s="28" t="s">
+      <c r="B116" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="C116" s="17" t="s">
+      <c r="C116" s="16" t="s">
         <v>226</v>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8"/>
     </row>
-    <row r="117">
-      <c r="A117" s="16"/>
-      <c r="B117" s="28" t="s">
+    <row r="117" spans="1:5" ht="14.4">
+      <c r="A117" s="15"/>
+      <c r="B117" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="C117" s="25" t="s">
+      <c r="C117" s="24" t="s">
         <v>228</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:5" ht="14.4">
       <c r="A118" s="6"/>
-      <c r="B118" s="28" t="s">
+      <c r="B118" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="C118" s="25" t="s">
+      <c r="C118" s="24" t="s">
         <v>230</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="8"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:5" ht="14.4">
       <c r="A119" s="6"/>
-      <c r="B119" s="28" t="s">
+      <c r="B119" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="C119" s="17" t="s">
+      <c r="C119" s="16" t="s">
         <v>232</v>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:5" ht="14.4">
       <c r="A120" s="6"/>
-      <c r="B120" s="28" t="s">
+      <c r="B120" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="C120" s="25" t="s">
+      <c r="C120" s="24" t="s">
         <v>234</v>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:5" ht="14.4">
       <c r="A121" s="6"/>
-      <c r="B121" s="28" t="s">
+      <c r="B121" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="C121" s="17" t="s">
+      <c r="C121" s="16" t="s">
         <v>236</v>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="8"/>
     </row>
-    <row r="122">
-      <c r="A122" s="23" t="s">
+    <row r="122" spans="1:5" ht="14.4">
+      <c r="A122" s="22" t="s">
         <v>237</v>
       </c>
-      <c r="B122" s="29" t="s">
+      <c r="B122" s="28" t="s">
         <v>238</v>
       </c>
-      <c r="C122" s="17" t="s">
+      <c r="C122" s="16" t="s">
         <v>239</v>
       </c>
       <c r="D122" s="8"/>
       <c r="E122" s="8"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:5" ht="14.4">
       <c r="A123" s="6"/>
-      <c r="B123" s="29" t="s">
+      <c r="B123" s="28" t="s">
         <v>240</v>
       </c>
-      <c r="C123" s="17" t="s">
+      <c r="C123" s="16" t="s">
         <v>241</v>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:5" ht="14.4">
       <c r="A124" s="6"/>
       <c r="B124" s="7" t="s">
         <v>242</v>
@@ -3333,599 +3317,599 @@
       <c r="D124" s="8"/>
       <c r="E124" s="8"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:5" ht="14.4">
       <c r="A125" s="6"/>
       <c r="B125" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="C125" s="25" t="s">
+      <c r="C125" s="24" t="s">
         <v>244</v>
       </c>
-      <c r="D125" s="17" t="s">
+      <c r="D125" s="16" t="s">
         <v>245</v>
       </c>
       <c r="E125" s="8"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:5" ht="14.4">
       <c r="A126" s="6"/>
       <c r="B126" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="C126" s="25" t="s">
+      <c r="C126" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="D126" s="17" t="s">
+      <c r="D126" s="16" t="s">
         <v>245</v>
       </c>
       <c r="E126" s="8"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:5" ht="14.4">
       <c r="A127" s="6"/>
       <c r="B127" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="C127" s="25" t="s">
+      <c r="C127" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="D127" s="17" t="s">
+      <c r="D127" s="16" t="s">
         <v>250</v>
       </c>
       <c r="E127" s="8"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:5" ht="14.4">
       <c r="A128" s="6"/>
       <c r="B128" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="C128" s="25" t="s">
+      <c r="C128" s="24" t="s">
         <v>252</v>
       </c>
-      <c r="D128" s="17" t="s">
+      <c r="D128" s="16" t="s">
         <v>250</v>
       </c>
       <c r="E128" s="8"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:5" ht="14.4">
       <c r="A129" s="6"/>
       <c r="B129" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="C129" s="25" t="s">
+      <c r="C129" s="24" t="s">
         <v>254</v>
       </c>
-      <c r="D129" s="17" t="s">
+      <c r="D129" s="16" t="s">
         <v>250</v>
       </c>
       <c r="E129" s="8"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:5" ht="14.4">
       <c r="A130" s="6"/>
       <c r="B130" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C130" s="25" t="s">
+      <c r="C130" s="24" t="s">
         <v>256</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:5" ht="14.4">
       <c r="A131" s="6"/>
       <c r="B131" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="C131" s="25" t="s">
+      <c r="C131" s="24" t="s">
         <v>258</v>
       </c>
-      <c r="D131" s="17" t="s">
+      <c r="D131" s="16" t="s">
         <v>259</v>
       </c>
       <c r="E131" s="8"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:5" ht="14.4">
       <c r="A132" s="6"/>
       <c r="B132" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="C132" s="17" t="s">
+      <c r="C132" s="16" t="s">
         <v>261</v>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:5" ht="14.4">
       <c r="A133" s="6"/>
       <c r="B133" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="C133" s="25" t="s">
+      <c r="C133" s="24" t="s">
         <v>263</v>
       </c>
       <c r="D133" s="8"/>
       <c r="E133" s="8"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:5" ht="14.4">
       <c r="A134" s="6"/>
-      <c r="B134" s="16" t="s">
+      <c r="B134" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="C134" s="17" t="s">
+      <c r="C134" s="16" t="s">
         <v>265</v>
       </c>
       <c r="D134" s="8"/>
       <c r="E134" s="8"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:5" ht="14.4">
       <c r="B135" s="7" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="18" t="s">
+    <row r="136" spans="1:5" ht="13.2">
+      <c r="A136" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="B136" s="19" t="s">
+      <c r="B136" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="C136" s="30" t="s">
+      <c r="C136" s="29" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="137">
-      <c r="B137" s="19" t="s">
+    <row r="137" spans="1:5" ht="13.2">
+      <c r="B137" s="34" t="s">
         <v>270</v>
       </c>
-      <c r="C137" s="30" t="s">
+      <c r="C137" s="29" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="138">
-      <c r="B138" s="19" t="s">
+    <row r="138" spans="1:5" ht="13.2">
+      <c r="B138" s="34" t="s">
         <v>272</v>
       </c>
-      <c r="C138" s="30" t="s">
+      <c r="C138" s="29" t="s">
         <v>273</v>
       </c>
-      <c r="D138" s="19" t="s">
+      <c r="D138" s="18" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="139">
-      <c r="B139" s="19" t="s">
+    <row r="139" spans="1:5" ht="13.2">
+      <c r="B139" s="34" t="s">
         <v>275</v>
       </c>
-      <c r="C139" s="30" t="s">
+      <c r="C139" s="29" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="140">
-      <c r="B140" s="19" t="s">
+    <row r="140" spans="1:5" ht="13.2">
+      <c r="B140" s="34" t="s">
         <v>277</v>
       </c>
-      <c r="C140" s="30" t="s">
+      <c r="C140" s="29" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="141">
-      <c r="B141" s="19" t="s">
+    <row r="141" spans="1:5" ht="13.2">
+      <c r="B141" s="34" t="s">
         <v>279</v>
       </c>
-      <c r="C141" s="30" t="s">
+      <c r="C141" s="29" t="s">
         <v>280</v>
       </c>
-      <c r="D141" s="19" t="s">
+      <c r="D141" s="18" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="31" t="s">
+    <row r="142" spans="1:5" ht="13.2">
+      <c r="A142" s="30" t="s">
         <v>281</v>
       </c>
-      <c r="B142" s="19" t="s">
+      <c r="B142" s="34" t="s">
         <v>282</v>
       </c>
-      <c r="C142" s="30" t="s">
+      <c r="C142" s="29" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="143">
-      <c r="B143" s="19" t="s">
+    <row r="143" spans="1:5" ht="13.2">
+      <c r="B143" s="34" t="s">
         <v>284</v>
       </c>
-      <c r="C143" s="30" t="s">
+      <c r="C143" s="29" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="144">
-      <c r="B144" s="19" t="s">
+    <row r="144" spans="1:5" ht="13.2">
+      <c r="B144" s="34" t="s">
         <v>286</v>
       </c>
-      <c r="C144" s="30" t="s">
+      <c r="C144" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="D144" s="19" t="s">
+      <c r="D144" s="18" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="145">
-      <c r="B145" s="19" t="s">
+    <row r="145" spans="1:3" ht="13.2">
+      <c r="B145" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="C145" s="32" t="s">
+      <c r="C145" s="31" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="146">
-      <c r="B146" s="19" t="s">
+    <row r="146" spans="1:3" ht="13.2">
+      <c r="B146" s="18" t="s">
         <v>290</v>
       </c>
-      <c r="C146" s="32" t="s">
+      <c r="C146" s="31" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="31" t="s">
+    <row r="147" spans="1:3" ht="13.2">
+      <c r="A147" s="30" t="s">
         <v>292</v>
       </c>
-      <c r="B147" s="19" t="s">
+      <c r="B147" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="C147" s="30" t="s">
+      <c r="C147" s="29" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="148">
-      <c r="B148" s="19" t="s">
+    <row r="148" spans="1:3" ht="13.2">
+      <c r="B148" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="C148" s="30" t="s">
+      <c r="C148" s="29" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="149">
-      <c r="B149" s="19" t="s">
+    <row r="149" spans="1:3" ht="13.2">
+      <c r="B149" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="C149" s="30" t="s">
+      <c r="C149" s="29" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="150">
-      <c r="B150" s="19" t="s">
+    <row r="150" spans="1:3" ht="13.2">
+      <c r="B150" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="C150" s="32" t="s">
+      <c r="C150" s="31" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="151">
-      <c r="B151" s="19" t="s">
+    <row r="151" spans="1:3" ht="13.2">
+      <c r="B151" s="18" t="s">
         <v>301</v>
       </c>
-      <c r="C151" s="30" t="s">
+      <c r="C151" s="29" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="152">
-      <c r="B152" s="19" t="s">
+    <row r="152" spans="1:3" ht="13.2">
+      <c r="B152" s="18" t="s">
         <v>303</v>
       </c>
-      <c r="C152" s="32" t="s">
+      <c r="C152" s="31" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="31" t="s">
+    <row r="153" spans="1:3" ht="13.2">
+      <c r="A153" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="B153" s="19" t="s">
+      <c r="B153" s="18" t="s">
         <v>306</v>
       </c>
-      <c r="C153" s="30" t="s">
+      <c r="C153" s="29" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="154">
-      <c r="B154" s="19" t="s">
+    <row r="154" spans="1:3" ht="13.2">
+      <c r="B154" s="18" t="s">
         <v>308</v>
       </c>
-      <c r="C154" s="30" t="s">
+      <c r="C154" s="29" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="155">
-      <c r="B155" s="19" t="s">
+    <row r="155" spans="1:3" ht="13.2">
+      <c r="B155" s="18" t="s">
         <v>310</v>
       </c>
-      <c r="C155" s="30" t="s">
+      <c r="C155" s="29" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="156">
-      <c r="B156" s="19" t="s">
+    <row r="156" spans="1:3" ht="13.2">
+      <c r="B156" s="18" t="s">
         <v>312</v>
       </c>
-      <c r="C156" s="30" t="s">
+      <c r="C156" s="29" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="157">
-      <c r="B157" s="19" t="s">
+    <row r="157" spans="1:3" ht="13.2">
+      <c r="B157" s="18" t="s">
         <v>314</v>
       </c>
-      <c r="C157" s="30" t="s">
+      <c r="C157" s="29" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="158">
-      <c r="B158" s="19" t="s">
+    <row r="158" spans="1:3" ht="13.2">
+      <c r="B158" s="18" t="s">
         <v>316</v>
       </c>
-      <c r="C158" s="30" t="s">
+      <c r="C158" s="29" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="159">
-      <c r="B159" s="19" t="s">
+    <row r="159" spans="1:3" ht="13.2">
+      <c r="B159" s="18" t="s">
         <v>318</v>
       </c>
-      <c r="C159" s="30" t="s">
+      <c r="C159" s="29" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="31" t="s">
+    <row r="160" spans="1:3" ht="13.2">
+      <c r="A160" s="30" t="s">
         <v>320</v>
       </c>
-      <c r="B160" s="19" t="s">
+      <c r="B160" s="18" t="s">
         <v>321</v>
       </c>
-      <c r="C160" s="30" t="s">
+      <c r="C160" s="29" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="161">
-      <c r="B161" s="19" t="s">
+    <row r="161" spans="1:3" ht="13.2">
+      <c r="B161" s="18" t="s">
         <v>323</v>
       </c>
-      <c r="C161" s="30" t="s">
+      <c r="C161" s="29" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="162">
-      <c r="B162" s="19" t="s">
+    <row r="162" spans="1:3" ht="13.2">
+      <c r="B162" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="C162" s="30" t="s">
+      <c r="C162" s="29" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="163">
-      <c r="B163" s="19" t="s">
+    <row r="163" spans="1:3" ht="13.2">
+      <c r="B163" s="18" t="s">
         <v>327</v>
       </c>
-      <c r="C163" s="32" t="s">
+      <c r="C163" s="31" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="31" t="s">
+    <row r="164" spans="1:3" ht="13.2">
+      <c r="A164" s="30" t="s">
         <v>329</v>
       </c>
-      <c r="B164" s="19" t="s">
+      <c r="B164" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="C164" s="30" t="s">
+      <c r="C164" s="29" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="165">
-      <c r="B165" s="19" t="s">
+    <row r="165" spans="1:3" ht="13.2">
+      <c r="B165" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="C165" s="32" t="s">
+      <c r="C165" s="31" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="166">
-      <c r="B166" s="19" t="s">
+    <row r="166" spans="1:3" ht="13.2">
+      <c r="B166" s="18" t="s">
         <v>334</v>
       </c>
-      <c r="C166" s="32" t="s">
+      <c r="C166" s="31" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="167">
-      <c r="B167" s="33" t="s">
+    <row r="167" spans="1:3" ht="13.2">
+      <c r="B167" s="32" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="168">
-      <c r="B168" s="18" t="s">
+    <row r="168" spans="1:3" ht="13.2">
+      <c r="B168" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="C168" s="30" t="s">
+      <c r="C168" s="29" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="169">
-      <c r="B169" s="18" t="s">
+    <row r="169" spans="1:3" ht="13.2">
+      <c r="B169" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="C169" s="30" t="s">
+      <c r="C169" s="29" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="170">
-      <c r="B170" s="18" t="s">
+    <row r="170" spans="1:3" ht="13.2">
+      <c r="B170" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="C170" s="30" t="s">
+      <c r="C170" s="29" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="171">
-      <c r="B171" s="18" t="s">
+    <row r="171" spans="1:3" ht="13.2">
+      <c r="B171" s="17" t="s">
         <v>343</v>
       </c>
-      <c r="C171" s="30" t="s">
+      <c r="C171" s="29" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="172">
-      <c r="B172" s="18" t="s">
+    <row r="172" spans="1:3" ht="13.2">
+      <c r="B172" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="C172" s="30" t="s">
+      <c r="C172" s="29" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="173">
-      <c r="B173" s="18" t="s">
+    <row r="173" spans="1:3" ht="13.2">
+      <c r="B173" s="17" t="s">
         <v>347</v>
       </c>
-      <c r="C173" s="30" t="s">
+      <c r="C173" s="29" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="174">
-      <c r="B174" s="18" t="s">
+    <row r="174" spans="1:3" ht="13.2">
+      <c r="B174" s="17" t="s">
         <v>349</v>
       </c>
-      <c r="C174" s="30" t="s">
+      <c r="C174" s="29" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="175">
-      <c r="B175" s="18" t="s">
+    <row r="175" spans="1:3" ht="13.2">
+      <c r="B175" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="C175" s="30" t="s">
+      <c r="C175" s="29" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="176">
-      <c r="B176" s="18" t="s">
+    <row r="176" spans="1:3" ht="13.2">
+      <c r="B176" s="17" t="s">
         <v>353</v>
       </c>
-      <c r="C176" s="30" t="s">
+      <c r="C176" s="29" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="177">
-      <c r="B177" s="18" t="s">
+    <row r="177" spans="2:3" ht="13.2">
+      <c r="B177" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="C177" s="30" t="s">
+      <c r="C177" s="29" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="178">
-      <c r="B178" s="18" t="s">
+    <row r="178" spans="2:3" ht="13.2">
+      <c r="B178" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="C178" s="30" t="s">
+      <c r="C178" s="29" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="179">
-      <c r="B179" s="18" t="s">
+    <row r="179" spans="2:3" ht="13.2">
+      <c r="B179" s="17" t="s">
         <v>359</v>
       </c>
-      <c r="C179" s="30" t="s">
+      <c r="C179" s="29" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="180">
-      <c r="B180" s="18" t="s">
+    <row r="180" spans="2:3" ht="13.2">
+      <c r="B180" s="17" t="s">
         <v>361</v>
       </c>
-      <c r="C180" s="30" t="s">
+      <c r="C180" s="29" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="181">
-      <c r="B181" s="18" t="s">
+    <row r="181" spans="2:3" ht="13.2">
+      <c r="B181" s="17" t="s">
         <v>363</v>
       </c>
-      <c r="C181" s="30" t="s">
+      <c r="C181" s="29" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="182">
-      <c r="B182" s="18" t="s">
+    <row r="182" spans="2:3" ht="13.2">
+      <c r="B182" s="17" t="s">
         <v>365</v>
       </c>
-      <c r="C182" s="30" t="s">
+      <c r="C182" s="29" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="183">
-      <c r="B183" s="18" t="s">
+    <row r="183" spans="2:3" ht="13.2">
+      <c r="B183" s="17" t="s">
         <v>367</v>
       </c>
-      <c r="C183" s="30" t="s">
+      <c r="C183" s="29" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="184">
-      <c r="B184" s="18" t="s">
+    <row r="184" spans="2:3" ht="13.2">
+      <c r="B184" s="17" t="s">
         <v>369</v>
       </c>
-      <c r="C184" s="30" t="s">
+      <c r="C184" s="29" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="185">
-      <c r="B185" s="18" t="s">
+    <row r="185" spans="2:3" ht="13.2">
+      <c r="B185" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="C185" s="30" t="s">
+      <c r="C185" s="29" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="186">
-      <c r="B186" s="18" t="s">
+    <row r="186" spans="2:3" ht="13.2">
+      <c r="B186" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="C186" s="30" t="s">
+      <c r="C186" s="29" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="187">
-      <c r="B187" s="18" t="s">
+    <row r="187" spans="2:3" ht="13.2">
+      <c r="B187" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="C187" s="30" t="s">
+      <c r="C187" s="29" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="188">
-      <c r="B188" s="33" t="s">
+    <row r="188" spans="2:3" ht="13.2">
+      <c r="B188" s="32" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="189">
-      <c r="B189" s="18" t="s">
+    <row r="189" spans="2:3" ht="13.2">
+      <c r="B189" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="C189" s="30" t="s">
+      <c r="C189" s="29" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="190">
-      <c r="B190" s="18" t="s">
+    <row r="190" spans="2:3" ht="13.2">
+      <c r="B190" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="C190" s="30" t="s">
+      <c r="C190" s="29" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="191">
-      <c r="B191" s="18" t="s">
+    <row r="191" spans="2:3" ht="13.2">
+      <c r="B191" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="C191" s="30" t="s">
+      <c r="C191" s="29" t="s">
         <v>382</v>
       </c>
     </row>
@@ -3935,192 +3919,192 @@
     <mergeCell ref="C56:D56"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="A1"/>
-    <hyperlink r:id="rId2" ref="C4"/>
-    <hyperlink r:id="rId3" ref="C5"/>
-    <hyperlink r:id="rId4" ref="C6"/>
-    <hyperlink r:id="rId5" ref="D6"/>
-    <hyperlink r:id="rId6" ref="E6"/>
-    <hyperlink r:id="rId7" ref="C7"/>
-    <hyperlink r:id="rId8" ref="C8"/>
-    <hyperlink r:id="rId9" ref="C9"/>
-    <hyperlink r:id="rId10" ref="C10"/>
-    <hyperlink r:id="rId11" ref="C11"/>
-    <hyperlink r:id="rId12" ref="C12"/>
-    <hyperlink r:id="rId13" ref="C13"/>
-    <hyperlink r:id="rId14" ref="C14"/>
-    <hyperlink r:id="rId15" ref="C15"/>
-    <hyperlink r:id="rId16" ref="D15"/>
-    <hyperlink r:id="rId17" ref="C17"/>
-    <hyperlink r:id="rId18" ref="C18"/>
-    <hyperlink r:id="rId19" ref="C19"/>
-    <hyperlink r:id="rId20" ref="C20"/>
-    <hyperlink r:id="rId21" ref="C21"/>
-    <hyperlink r:id="rId22" ref="C22"/>
-    <hyperlink r:id="rId23" ref="C23"/>
-    <hyperlink r:id="rId24" ref="C24"/>
-    <hyperlink r:id="rId25" ref="C26"/>
-    <hyperlink r:id="rId26" ref="C27"/>
-    <hyperlink r:id="rId27" ref="C28"/>
-    <hyperlink r:id="rId28" ref="C29"/>
-    <hyperlink r:id="rId29" ref="C30"/>
-    <hyperlink r:id="rId30" ref="C31"/>
-    <hyperlink r:id="rId31" ref="C32"/>
-    <hyperlink r:id="rId32" ref="C33"/>
-    <hyperlink r:id="rId33" ref="C34"/>
-    <hyperlink r:id="rId34" ref="C35"/>
-    <hyperlink r:id="rId35" ref="C36"/>
-    <hyperlink r:id="rId36" ref="C37"/>
-    <hyperlink r:id="rId37" ref="C39"/>
-    <hyperlink r:id="rId38" ref="C40"/>
-    <hyperlink r:id="rId39" ref="C41"/>
-    <hyperlink r:id="rId40" ref="C42"/>
-    <hyperlink r:id="rId41" ref="C43"/>
-    <hyperlink r:id="rId42" ref="C44"/>
-    <hyperlink r:id="rId43" ref="C46"/>
-    <hyperlink r:id="rId44" ref="C47"/>
-    <hyperlink r:id="rId45" ref="C48"/>
-    <hyperlink r:id="rId46" ref="C49"/>
-    <hyperlink r:id="rId47" ref="C50"/>
-    <hyperlink r:id="rId48" ref="C51"/>
-    <hyperlink r:id="rId49" ref="C53"/>
-    <hyperlink r:id="rId50" ref="C54"/>
-    <hyperlink r:id="rId51" ref="C55"/>
-    <hyperlink r:id="rId52" ref="C56"/>
-    <hyperlink r:id="rId53" ref="C57"/>
-    <hyperlink r:id="rId54" ref="C58"/>
-    <hyperlink r:id="rId55" ref="C59"/>
-    <hyperlink r:id="rId56" ref="C61"/>
-    <hyperlink r:id="rId57" ref="C62"/>
-    <hyperlink r:id="rId58" ref="C63"/>
-    <hyperlink r:id="rId59" ref="C64"/>
-    <hyperlink r:id="rId60" ref="C65"/>
-    <hyperlink r:id="rId61" ref="C66"/>
-    <hyperlink r:id="rId62" ref="B68"/>
-    <hyperlink r:id="rId63" ref="C68"/>
-    <hyperlink r:id="rId64" ref="C69"/>
-    <hyperlink r:id="rId65" ref="C71"/>
-    <hyperlink r:id="rId66" ref="C72"/>
-    <hyperlink r:id="rId67" ref="C73"/>
-    <hyperlink r:id="rId68" ref="C74"/>
-    <hyperlink r:id="rId69" ref="C75"/>
-    <hyperlink r:id="rId70" ref="C76"/>
-    <hyperlink r:id="rId71" ref="C78"/>
-    <hyperlink r:id="rId72" ref="C79"/>
-    <hyperlink r:id="rId73" ref="C80"/>
-    <hyperlink r:id="rId74" ref="C81"/>
-    <hyperlink r:id="rId75" ref="C83"/>
-    <hyperlink r:id="rId76" ref="C84"/>
-    <hyperlink r:id="rId77" ref="C85"/>
-    <hyperlink r:id="rId78" ref="C86"/>
-    <hyperlink r:id="rId79" ref="C87"/>
-    <hyperlink r:id="rId80" ref="C88"/>
-    <hyperlink r:id="rId81" ref="C89"/>
-    <hyperlink r:id="rId82" ref="C90"/>
-    <hyperlink r:id="rId83" ref="C91"/>
-    <hyperlink r:id="rId84" ref="C92"/>
-    <hyperlink r:id="rId85" ref="C93"/>
-    <hyperlink r:id="rId86" ref="C94"/>
-    <hyperlink r:id="rId87" ref="C95"/>
-    <hyperlink r:id="rId88" ref="B96"/>
-    <hyperlink r:id="rId89" ref="C96"/>
-    <hyperlink r:id="rId90" ref="C97"/>
-    <hyperlink r:id="rId91" ref="C98"/>
-    <hyperlink r:id="rId92" ref="C99"/>
-    <hyperlink r:id="rId93" ref="C100"/>
-    <hyperlink r:id="rId94" ref="C101"/>
-    <hyperlink r:id="rId95" ref="C102"/>
-    <hyperlink r:id="rId96" ref="C103"/>
-    <hyperlink r:id="rId97" ref="C104"/>
-    <hyperlink r:id="rId98" ref="C105"/>
-    <hyperlink r:id="rId99" ref="C107"/>
-    <hyperlink r:id="rId100" ref="C108"/>
-    <hyperlink r:id="rId101" ref="C109"/>
-    <hyperlink r:id="rId102" ref="C110"/>
-    <hyperlink r:id="rId103" ref="C111"/>
-    <hyperlink r:id="rId104" ref="C112"/>
-    <hyperlink r:id="rId105" ref="C113"/>
-    <hyperlink r:id="rId106" ref="C114"/>
-    <hyperlink r:id="rId107" ref="C115"/>
-    <hyperlink r:id="rId108" ref="C116"/>
-    <hyperlink r:id="rId109" ref="C117"/>
-    <hyperlink r:id="rId110" ref="C118"/>
-    <hyperlink r:id="rId111" ref="C119"/>
-    <hyperlink r:id="rId112" ref="C120"/>
-    <hyperlink r:id="rId113" ref="C121"/>
-    <hyperlink r:id="rId114" ref="C122"/>
-    <hyperlink r:id="rId115" ref="C123"/>
-    <hyperlink r:id="rId116" ref="C125"/>
-    <hyperlink r:id="rId117" ref="D125"/>
-    <hyperlink r:id="rId118" ref="C126"/>
-    <hyperlink r:id="rId119" ref="D126"/>
-    <hyperlink r:id="rId120" ref="C127"/>
-    <hyperlink r:id="rId121" ref="D127"/>
-    <hyperlink r:id="rId122" ref="C128"/>
-    <hyperlink r:id="rId123" ref="D128"/>
-    <hyperlink r:id="rId124" ref="C129"/>
-    <hyperlink r:id="rId125" ref="D129"/>
-    <hyperlink r:id="rId126" ref="C130"/>
-    <hyperlink r:id="rId127" ref="C131"/>
-    <hyperlink r:id="rId128" ref="D131"/>
-    <hyperlink r:id="rId129" ref="C132"/>
-    <hyperlink r:id="rId130" ref="C133"/>
-    <hyperlink r:id="rId131" ref="C134"/>
-    <hyperlink r:id="rId132" ref="C136"/>
-    <hyperlink r:id="rId133" ref="C137"/>
-    <hyperlink r:id="rId134" ref="C138"/>
-    <hyperlink r:id="rId135" ref="C139"/>
-    <hyperlink r:id="rId136" ref="C140"/>
-    <hyperlink r:id="rId137" ref="C141"/>
-    <hyperlink r:id="rId138" ref="C142"/>
-    <hyperlink r:id="rId139" ref="C143"/>
-    <hyperlink r:id="rId140" ref="C144"/>
-    <hyperlink r:id="rId141" ref="C145"/>
-    <hyperlink r:id="rId142" ref="C146"/>
-    <hyperlink r:id="rId143" ref="C147"/>
-    <hyperlink r:id="rId144" ref="C148"/>
-    <hyperlink r:id="rId145" ref="C149"/>
-    <hyperlink r:id="rId146" ref="C150"/>
-    <hyperlink r:id="rId147" ref="C151"/>
-    <hyperlink r:id="rId148" ref="C152"/>
-    <hyperlink r:id="rId149" ref="C153"/>
-    <hyperlink r:id="rId150" ref="C154"/>
-    <hyperlink r:id="rId151" ref="C155"/>
-    <hyperlink r:id="rId152" ref="C156"/>
-    <hyperlink r:id="rId153" ref="C157"/>
-    <hyperlink r:id="rId154" ref="C158"/>
-    <hyperlink r:id="rId155" ref="C159"/>
-    <hyperlink r:id="rId156" ref="C160"/>
-    <hyperlink r:id="rId157" ref="C161"/>
-    <hyperlink r:id="rId158" ref="C162"/>
-    <hyperlink r:id="rId159" ref="C163"/>
-    <hyperlink r:id="rId160" ref="C164"/>
-    <hyperlink r:id="rId161" ref="C165"/>
-    <hyperlink r:id="rId162" ref="C166"/>
-    <hyperlink r:id="rId163" ref="C168"/>
-    <hyperlink r:id="rId164" ref="C169"/>
-    <hyperlink r:id="rId165" ref="C170"/>
-    <hyperlink r:id="rId166" ref="C171"/>
-    <hyperlink r:id="rId167" ref="C172"/>
-    <hyperlink r:id="rId168" ref="C173"/>
-    <hyperlink r:id="rId169" ref="C174"/>
-    <hyperlink r:id="rId170" ref="C175"/>
-    <hyperlink r:id="rId171" ref="C176"/>
-    <hyperlink r:id="rId172" ref="C177"/>
-    <hyperlink r:id="rId173" ref="C178"/>
-    <hyperlink r:id="rId174" ref="C179"/>
-    <hyperlink r:id="rId175" ref="C180"/>
-    <hyperlink r:id="rId176" ref="C181"/>
-    <hyperlink r:id="rId177" ref="C182"/>
-    <hyperlink r:id="rId178" ref="C183"/>
-    <hyperlink r:id="rId179" ref="C184"/>
-    <hyperlink r:id="rId180" ref="C185"/>
-    <hyperlink r:id="rId181" ref="C186"/>
-    <hyperlink r:id="rId182" ref="C187"/>
-    <hyperlink r:id="rId183" ref="C189"/>
-    <hyperlink r:id="rId184" ref="C190"/>
-    <hyperlink r:id="rId185" ref="C191"/>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="E6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C7" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="C8" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="C9" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="C10" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="C11" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="C12" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="C13" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="C14" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="C15" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="D15" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="C17" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="C18" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="C19" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="C20" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="C21" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="C22" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="C23" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="C24" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="C26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="C27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="C28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="C29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="C30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="C31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="C32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="C33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="C34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="C35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="C36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="C37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="C39" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="C40" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="C41" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="C42" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="C43" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="C44" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="C46" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="C47" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="C48" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="C49" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="C50" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="C51" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="C53" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="C54" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="C55" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="C56" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="C57" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="C58" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="C59" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="C61" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="C62" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="C63" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="C64" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="C65" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="C66" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="B68" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="C68" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="C69" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="C71" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="C72" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="C73" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="C74" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="C75" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="C76" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="C78" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="C79" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="C80" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="C81" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="C83" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="C84" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="C85" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="C86" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="C87" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="C88" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="C89" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="C90" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="C91" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="C92" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="C93" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="C94" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="C95" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="B96" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="C96" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="C97" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="C98" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="C99" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="C100" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="C101" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="C102" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="C103" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="C104" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="C105" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="C107" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="C108" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="C109" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="C110" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="C111" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="C112" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="C113" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="C114" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="C115" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="C116" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="C117" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="C118" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="C119" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="C120" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="C121" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="C122" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="C123" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="C125" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="D125" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="C126" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="D126" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="C127" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="D127" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="C128" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="D128" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="C129" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="D129" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="C130" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="C131" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="D131" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="C132" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="C133" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="C134" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="C136" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="C137" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="C138" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="C139" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="C140" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="C141" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="C142" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="C143" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="C144" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="C145" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="C146" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="C147" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="C148" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="C149" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="C150" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="C151" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="C152" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="C153" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="C154" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="C155" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="C156" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="C157" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="C158" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="C159" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="C160" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="C161" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="C162" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="C163" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="C164" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="C165" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="C166" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="C168" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="C169" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="C170" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="C171" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="C172" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="C173" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="C174" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="C175" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="C176" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="C177" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="C178" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="C179" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="C180" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="C181" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="C182" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="C183" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="C184" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="C185" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="C186" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="C187" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="C189" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="C190" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="C191" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
   </hyperlinks>
-  <drawing r:id="rId186"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>